--- a/USC_AI_Guided_Tour_Database.xlsx
+++ b/USC_AI_Guided_Tour_Database.xlsx
@@ -2,12 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schema" sheetId="1" r:id="R5dd5c9d4eb464afa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buildings" sheetId="2" r:id="R0422a9078b404329"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BuildingEvents" sheetId="3" r:id="R32c16ffb6d9149c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="4" r:id="R989d059886824333"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SourceLinks" sheetId="5" r:id="R12556e4b61624113"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BuildingPhotos" sheetId="6" r:id="R1aeb99d113e44c21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schema" sheetId="1" r:id="Rb5be12a02d7a4a0c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buildings" sheetId="2" r:id="R3b9aeea34ce64fd2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BuildingEvents" sheetId="3" r:id="Rf1ad2c8f23a641d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="4" r:id="R323bcbcde29248ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SourceLinks" sheetId="5" r:id="R1ce704e19f254be7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BuildingPhotos" sheetId="6" r:id="R1eb69a2450894bc8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LocalizedContent" sheetId="7" r:id="R3f061b28d2914982"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -38,12 +39,17 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -93,7 +99,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="17">
+  <x:cellXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -164,6 +170,30 @@
         </x:ext>
       </x:extLst>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="0"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -189,8 +219,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SchemaTable" displayName="SchemaTable" ref="A1:F58" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:F58"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SchemaTable" displayName="SchemaTable" ref="A1:F71" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:F71"/>
   <x:tableColumns count="6">
     <x:tableColumn id="1" name="table_name"/>
     <x:tableColumn id="2" name="column_name"/>
@@ -300,6 +330,28 @@
     <x:tableColumn id="14" name="alt_text"/>
     <x:tableColumn id="15" name="chatbot_use_note"/>
     <x:tableColumn id="16" name="verified_on"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="LocalizedContentTable" displayName="LocalizedContentTable" ref="A1:M28" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:M28"/>
+  <x:tableColumns count="13">
+    <x:tableColumn id="1" name="content_id"/>
+    <x:tableColumn id="2" name="building_id"/>
+    <x:tableColumn id="3" name="language_code"/>
+    <x:tableColumn id="4" name="language_name"/>
+    <x:tableColumn id="5" name="reading_level"/>
+    <x:tableColumn id="6" name="reading_level_label"/>
+    <x:tableColumn id="7" name="reading_level_order"/>
+    <x:tableColumn id="8" name="display_name"/>
+    <x:tableColumn id="9" name="short_summary"/>
+    <x:tableColumn id="10" name="full_description"/>
+    <x:tableColumn id="11" name="key_facts"/>
+    <x:tableColumn id="12" name="translation_status"/>
+    <x:tableColumn id="13" name="record_as_of"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -1577,10 +1629,248 @@
         <x:v>Date the links and rights metadata were checked</x:v>
       </x:c>
     </x:row>
+    <x:row r="59">
+      <x:c r="A59" t="str">
+        <x:v>LocalizedContent</x:v>
+      </x:c>
+      <x:c r="B59" t="str">
+        <x:v>content_id</x:v>
+      </x:c>
+      <x:c r="C59" t="str">
+        <x:v>VARCHAR(50)</x:v>
+      </x:c>
+      <x:c r="D59" t="str">
+        <x:v>PRIMARY KEY</x:v>
+      </x:c>
+      <x:c r="E59" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="F59" t="str">
+        <x:v>Stable identifier combining building, language, and reading level</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" t="str">
+        <x:v>LocalizedContent</x:v>
+      </x:c>
+      <x:c r="B60" t="str">
+        <x:v>building_id</x:v>
+      </x:c>
+      <x:c r="C60" t="str">
+        <x:v>VARCHAR(20)</x:v>
+      </x:c>
+      <x:c r="D60" t="str">
+        <x:v>FOREIGN KEY</x:v>
+      </x:c>
+      <x:c r="E60" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="F60" t="str">
+        <x:v>References Buildings.building_id</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" t="str">
+        <x:v>LocalizedContent</x:v>
+      </x:c>
+      <x:c r="B61" t="str">
+        <x:v>language_code</x:v>
+      </x:c>
+      <x:c r="C61" t="str">
+        <x:v>CHAR(2)</x:v>
+      </x:c>
+      <x:c r="D61" t="str"/>
+      <x:c r="E61" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="F61" t="str">
+        <x:v>ISO 639-1 language code: en, es, or fr</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" t="str">
+        <x:v>LocalizedContent</x:v>
+      </x:c>
+      <x:c r="B62" t="str">
+        <x:v>language_name</x:v>
+      </x:c>
+      <x:c r="C62" t="str">
+        <x:v>VARCHAR(30)</x:v>
+      </x:c>
+      <x:c r="D62" t="str"/>
+      <x:c r="E62" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="F62" t="str">
+        <x:v>Human-readable language name</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" t="str">
+        <x:v>LocalizedContent</x:v>
+      </x:c>
+      <x:c r="B63" t="str">
+        <x:v>reading_level</x:v>
+      </x:c>
+      <x:c r="C63" t="str">
+        <x:v>VARCHAR(20)</x:v>
+      </x:c>
+      <x:c r="D63" t="str"/>
+      <x:c r="E63" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="F63" t="str">
+        <x:v>Program key: college, secondary, or elementary</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" t="str">
+        <x:v>LocalizedContent</x:v>
+      </x:c>
+      <x:c r="B64" t="str">
+        <x:v>reading_level_label</x:v>
+      </x:c>
+      <x:c r="C64" t="str">
+        <x:v>VARCHAR(50)</x:v>
+      </x:c>
+      <x:c r="D64" t="str"/>
+      <x:c r="E64" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="F64" t="str">
+        <x:v>Localized reading-level label for display</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" t="str">
+        <x:v>LocalizedContent</x:v>
+      </x:c>
+      <x:c r="B65" t="str">
+        <x:v>reading_level_order</x:v>
+      </x:c>
+      <x:c r="C65" t="str">
+        <x:v>SMALLINT</x:v>
+      </x:c>
+      <x:c r="D65" t="str"/>
+      <x:c r="E65" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="F65" t="str">
+        <x:v>Sort order: 1 elementary, 2 secondary, 3 college</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" t="str">
+        <x:v>LocalizedContent</x:v>
+      </x:c>
+      <x:c r="B66" t="str">
+        <x:v>display_name</x:v>
+      </x:c>
+      <x:c r="C66" t="str">
+        <x:v>VARCHAR(150)</x:v>
+      </x:c>
+      <x:c r="D66" t="str"/>
+      <x:c r="E66" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="F66" t="str">
+        <x:v>Localized building name for display</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" t="str">
+        <x:v>LocalizedContent</x:v>
+      </x:c>
+      <x:c r="B67" t="str">
+        <x:v>short_summary</x:v>
+      </x:c>
+      <x:c r="C67" t="str">
+        <x:v>TEXT</x:v>
+      </x:c>
+      <x:c r="D67" t="str"/>
+      <x:c r="E67" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="F67" t="str">
+        <x:v>Brief localized description for cards or search results</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" t="str">
+        <x:v>LocalizedContent</x:v>
+      </x:c>
+      <x:c r="B68" t="str">
+        <x:v>full_description</x:v>
+      </x:c>
+      <x:c r="C68" t="str">
+        <x:v>TEXT</x:v>
+      </x:c>
+      <x:c r="D68" t="str"/>
+      <x:c r="E68" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="F68" t="str">
+        <x:v>Complete localized narrative adapted to the selected reading level</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" t="str">
+        <x:v>LocalizedContent</x:v>
+      </x:c>
+      <x:c r="B69" t="str">
+        <x:v>key_facts</x:v>
+      </x:c>
+      <x:c r="C69" t="str">
+        <x:v>TEXT</x:v>
+      </x:c>
+      <x:c r="D69" t="str"/>
+      <x:c r="E69" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="F69" t="str">
+        <x:v>Localized semicolon-separated facts for quick answers</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" t="str">
+        <x:v>LocalizedContent</x:v>
+      </x:c>
+      <x:c r="B70" t="str">
+        <x:v>translation_status</x:v>
+      </x:c>
+      <x:c r="C70" t="str">
+        <x:v>VARCHAR(80)</x:v>
+      </x:c>
+      <x:c r="D70" t="str"/>
+      <x:c r="E70" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="F70" t="str">
+        <x:v>Content provenance and review status</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" t="str">
+        <x:v>LocalizedContent</x:v>
+      </x:c>
+      <x:c r="B71" t="str">
+        <x:v>record_as_of</x:v>
+      </x:c>
+      <x:c r="C71" t="str">
+        <x:v>DATE</x:v>
+      </x:c>
+      <x:c r="D71" t="str"/>
+      <x:c r="E71" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="F71" t="str">
+        <x:v>Date through which factual content was checked</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f463456e1144a64"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11ac0fbf51414b20"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1840,7 +2130,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R23ff757722354dd2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc8b6ceced4a24c83"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2563,7 +2853,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7adba5115cb1448a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ecd056f74e24a94"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3038,7 +3328,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R28ccadad6ea04652"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3dc41552b3348e7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3490,7 +3780,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00a6e0f3f08249c0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc8f7ef3d4f574e10"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4153,7 +4443,1185 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54a344c1c8114e03"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra5b7cb12fb0943a0"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FF70AD47"/>
+  </x:sheetPr>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="30" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="30" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="34" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="58" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="100" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="76" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="52" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="16" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="34" customHeight="1">
+      <x:c r="A1" s="22" t="str">
+        <x:v>content_id</x:v>
+      </x:c>
+      <x:c r="B1" s="22" t="str">
+        <x:v>building_id</x:v>
+      </x:c>
+      <x:c r="C1" s="22" t="str">
+        <x:v>language_code</x:v>
+      </x:c>
+      <x:c r="D1" s="22" t="str">
+        <x:v>language_name</x:v>
+      </x:c>
+      <x:c r="E1" s="22" t="str">
+        <x:v>reading_level</x:v>
+      </x:c>
+      <x:c r="F1" s="22" t="str">
+        <x:v>reading_level_label</x:v>
+      </x:c>
+      <x:c r="G1" s="22" t="str">
+        <x:v>reading_level_order</x:v>
+      </x:c>
+      <x:c r="H1" s="22" t="str">
+        <x:v>display_name</x:v>
+      </x:c>
+      <x:c r="I1" s="22" t="str">
+        <x:v>short_summary</x:v>
+      </x:c>
+      <x:c r="J1" s="22" t="str">
+        <x:v>full_description</x:v>
+      </x:c>
+      <x:c r="K1" s="22" t="str">
+        <x:v>key_facts</x:v>
+      </x:c>
+      <x:c r="L1" s="22" t="str">
+        <x:v>translation_status</x:v>
+      </x:c>
+      <x:c r="M1" s="22" t="str">
+        <x:v>record_as_of</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="200" customHeight="1">
+      <x:c r="A2" s="23" t="str">
+        <x:v>usc_bldg_001_en_college</x:v>
+      </x:c>
+      <x:c r="B2" s="23" t="str">
+        <x:v>usc_bldg_001</x:v>
+      </x:c>
+      <x:c r="C2" s="23" t="str">
+        <x:v>en</x:v>
+      </x:c>
+      <x:c r="D2" s="23" t="str">
+        <x:v>English</x:v>
+      </x:c>
+      <x:c r="E2" s="23" t="str">
+        <x:v>college</x:v>
+      </x:c>
+      <x:c r="F2" s="23" t="str">
+        <x:v>College level</x:v>
+      </x:c>
+      <x:c r="G2" s="24" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H2" s="14" t="str">
+        <x:v>Thomas Cooper Library</x:v>
+      </x:c>
+      <x:c r="I2" s="14" t="str">
+        <x:v>USC's principal student and research library, opened in 1959 and transformed by a four-level underground expansion in 1976.</x:v>
+      </x:c>
+      <x:c r="J2" s="14" t="str">
+        <x:v>Thomas Cooper Library opened in 1959 as a three-level Undergraduate Library designed by Edward Durell Stone, with two floors above ground, one below, and room for roughly 600 students. It was named for Thomas Cooper in 1968. Planning for growth began in 1969, excavation started in 1973, and a four-level underground addition opened in June 1976. The enlarged seven-level building contains 284,976 square feet, was designed for about 2,500 people and 1.5 million books, and became USC's primary library. It is regarded as the first freestanding undergraduate library in the South and as an important example of postwar, mid-century modern campus development. USC approved a $65 million phased renovation in December 2025. Perkins Eastman and Quackenbush Architects and Planners are leading work planned for 2027–2032 to modernize systems, safety, accessibility, study and teaching areas, and technology while retaining the building's architectural character.</x:v>
+      </x:c>
+      <x:c r="K2" s="14" t="str">
+        <x:v>Built and opened: 1959; Original architect: Edward Durell Stone; Named: 1968; Underground expansion opened: June 1976; Size: 284,976 sq. ft.; Major renovation: $65 million, planned 2027–2032; Renovation designers: Perkins Eastman and Quackenbush Architects and Planners</x:v>
+      </x:c>
+      <x:c r="L2" s="14" t="str">
+        <x:v>adapted_from_verified_source</x:v>
+      </x:c>
+      <x:c r="M2" s="14" t="str">
+        <x:v>2026-10-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="170" customHeight="1">
+      <x:c r="A3" s="23" t="str">
+        <x:v>usc_bldg_001_en_secondary</x:v>
+      </x:c>
+      <x:c r="B3" s="23" t="str">
+        <x:v>usc_bldg_001</x:v>
+      </x:c>
+      <x:c r="C3" s="23" t="str">
+        <x:v>en</x:v>
+      </x:c>
+      <x:c r="D3" s="23" t="str">
+        <x:v>English</x:v>
+      </x:c>
+      <x:c r="E3" s="23" t="str">
+        <x:v>secondary</x:v>
+      </x:c>
+      <x:c r="F3" s="23" t="str">
+        <x:v>Middle/High school</x:v>
+      </x:c>
+      <x:c r="G3" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H3" s="14" t="str">
+        <x:v>Thomas Cooper Library</x:v>
+      </x:c>
+      <x:c r="I3" s="14" t="str">
+        <x:v>Thomas Cooper Library opened in 1959 and became USC's main library after a large underground addition opened in 1976.</x:v>
+      </x:c>
+      <x:c r="J3" s="14" t="str">
+        <x:v>Thomas Cooper Library first opened in 1959 as the Undergraduate Library. Architect Edward Durell Stone designed the original three-level building for about 600 students. USC named it for Thomas Cooper in 1968. As the university grew, construction began on a major underground addition. Four new underground floors opened in June 1976, giving the library seven levels and 284,976 square feet. It could serve about 2,500 people and hold 1.5 million books. The building became USC's main library and is known as the first separate undergraduate library in the South. In December 2025, USC approved a $65 million renovation. Perkins Eastman and Quackenbush Architects and Planners are designing the phased project, planned for 2027 through about 2032. The work will improve utilities, safety, accessibility, study rooms, teaching areas, and technology while protecting the building's mid-century modern look.</x:v>
+      </x:c>
+      <x:c r="K3" s="14" t="str">
+        <x:v>Opened: 1959; Architect: Edward Durell Stone; Renamed: 1968; Major expansion: 1976; Seven levels; 284,976 sq. ft.; Renovation planned: 2027–2032</x:v>
+      </x:c>
+      <x:c r="L3" s="14" t="str">
+        <x:v>adapted_from_verified_source</x:v>
+      </x:c>
+      <x:c r="M3" s="14" t="str">
+        <x:v>2026-10-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="130" customHeight="1">
+      <x:c r="A4" s="23" t="str">
+        <x:v>usc_bldg_001_en_elementary</x:v>
+      </x:c>
+      <x:c r="B4" s="23" t="str">
+        <x:v>usc_bldg_001</x:v>
+      </x:c>
+      <x:c r="C4" s="23" t="str">
+        <x:v>en</x:v>
+      </x:c>
+      <x:c r="D4" s="23" t="str">
+        <x:v>English</x:v>
+      </x:c>
+      <x:c r="E4" s="23" t="str">
+        <x:v>elementary</x:v>
+      </x:c>
+      <x:c r="F4" s="23" t="str">
+        <x:v>Elementary school</x:v>
+      </x:c>
+      <x:c r="G4" s="24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H4" s="14" t="str">
+        <x:v>Thomas Cooper Library</x:v>
+      </x:c>
+      <x:c r="I4" s="14" t="str">
+        <x:v>Thomas Cooper Library is USC's main library. It opened in 1959 and grew much larger in 1976.</x:v>
+      </x:c>
+      <x:c r="J4" s="14" t="str">
+        <x:v>Thomas Cooper Library opened in 1959. Edward Durell Stone designed it. At first, it had three floors and space for about 600 students. USC gave the library its current name in 1968. In 1976, four new floors opened underground. The bigger library then had seven levels and became USC's main library. It is an important example of mid-century modern design. USC plans a large renovation from 2027 to about 2032. The project will make the library safer and easier to use. It will also improve study spaces, classrooms, and technology while keeping the building's special look.</x:v>
+      </x:c>
+      <x:c r="K4" s="14" t="str">
+        <x:v>Opened: 1959; Designer: Edward Durell Stone; New name: 1968; Underground floors opened: 1976; Seven levels; Renovation planned: 2027–2032</x:v>
+      </x:c>
+      <x:c r="L4" s="14" t="str">
+        <x:v>adapted_from_verified_source</x:v>
+      </x:c>
+      <x:c r="M4" s="14" t="str">
+        <x:v>2026-10-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="200" customHeight="1">
+      <x:c r="A5" s="23" t="str">
+        <x:v>usc_bldg_001_es_college</x:v>
+      </x:c>
+      <x:c r="B5" s="23" t="str">
+        <x:v>usc_bldg_001</x:v>
+      </x:c>
+      <x:c r="C5" s="23" t="str">
+        <x:v>es</x:v>
+      </x:c>
+      <x:c r="D5" s="23" t="str">
+        <x:v>Español</x:v>
+      </x:c>
+      <x:c r="E5" s="23" t="str">
+        <x:v>college</x:v>
+      </x:c>
+      <x:c r="F5" s="23" t="str">
+        <x:v>Nivel universitario</x:v>
+      </x:c>
+      <x:c r="G5" s="24" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H5" s="14" t="str">
+        <x:v>Biblioteca Thomas Cooper</x:v>
+      </x:c>
+      <x:c r="I5" s="14" t="str">
+        <x:v>Principal biblioteca de estudio e investigación de la USC, inaugurada en 1959 y transformada por una ampliación subterránea de cuatro niveles en 1976.</x:v>
+      </x:c>
+      <x:c r="J5" s="14" t="str">
+        <x:v>La Biblioteca Thomas Cooper abrió en 1959 como una biblioteca universitaria de tres niveles, diseñada por Edward Durell Stone, con dos plantas sobre el nivel del suelo, una subterránea y capacidad para unos 600 estudiantes. En 1968 recibió el nombre de Thomas Cooper. La planificación de su ampliación comenzó en 1969, la excavación empezó en 1973 y una adición de cuatro niveles subterráneos abrió en junio de 1976. El edificio ampliado tiene siete niveles y 284,976 pies cuadrados; fue diseñado para unas 2,500 personas y 1.5 millones de libros, y se convirtió en la biblioteca principal de la USC. Se considera la primera biblioteca independiente para estudiantes universitarios de pregrado en el sur de Estados Unidos y un ejemplo importante del desarrollo de posguerra y de la arquitectura moderna de mediados del siglo XX. En diciembre de 2025, la USC aprobó una renovación por fases de 65 millones de dólares. Perkins Eastman y Quackenbush Architects and Planners dirigen el proyecto previsto para 2027–2032, que modernizará los sistemas, la seguridad, la accesibilidad y los espacios de estudio, enseñanza y tecnología, conservando el carácter arquitectónico del edificio.</x:v>
+      </x:c>
+      <x:c r="K5" s="14" t="str">
+        <x:v>Construcción e inauguración: 1959; Arquitecto original: Edward Durell Stone; Nombre adoptado: 1968; Ampliación subterránea inaugurada: junio de 1976; Superficie: 284,976 pies cuadrados; Renovación: 65 millones de dólares, prevista para 2027–2032; Diseñadores: Perkins Eastman y Quackenbush Architects and Planners</x:v>
+      </x:c>
+      <x:c r="L5" s="14" t="str">
+        <x:v>translated_from_verified_english_human_review_recommended</x:v>
+      </x:c>
+      <x:c r="M5" s="14" t="str">
+        <x:v>2026-10-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="170" customHeight="1">
+      <x:c r="A6" s="23" t="str">
+        <x:v>usc_bldg_001_es_secondary</x:v>
+      </x:c>
+      <x:c r="B6" s="23" t="str">
+        <x:v>usc_bldg_001</x:v>
+      </x:c>
+      <x:c r="C6" s="23" t="str">
+        <x:v>es</x:v>
+      </x:c>
+      <x:c r="D6" s="23" t="str">
+        <x:v>Español</x:v>
+      </x:c>
+      <x:c r="E6" s="23" t="str">
+        <x:v>secondary</x:v>
+      </x:c>
+      <x:c r="F6" s="23" t="str">
+        <x:v>Escuela intermedia/secundaria</x:v>
+      </x:c>
+      <x:c r="G6" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H6" s="14" t="str">
+        <x:v>Biblioteca Thomas Cooper</x:v>
+      </x:c>
+      <x:c r="I6" s="14" t="str">
+        <x:v>La Biblioteca Thomas Cooper abrió en 1959 y se convirtió en la biblioteca principal de la USC después de una gran ampliación subterránea en 1976.</x:v>
+      </x:c>
+      <x:c r="J6" s="14" t="str">
+        <x:v>La Biblioteca Thomas Cooper abrió en 1959 como biblioteca para estudiantes universitarios. El arquitecto Edward Durell Stone diseñó el edificio original de tres niveles para unas 600 personas. En 1968, la USC le dio el nombre de Thomas Cooper. Cuando la universidad creció, comenzó una gran ampliación bajo tierra. Cuatro plantas subterráneas nuevas abrieron en junio de 1976. Así, la biblioteca llegó a tener siete niveles y 284,976 pies cuadrados, con espacio para unas 2,500 personas y 1.5 millones de libros. Se convirtió en la biblioteca principal de la USC y se reconoce como la primera biblioteca independiente para estudiantes de pregrado en el sur de Estados Unidos. En diciembre de 2025, la USC aprobó una renovación de 65 millones de dólares. Perkins Eastman y Quackenbush Architects and Planners diseñan el proyecto previsto para 2027–2032. Las obras mejorarán los servicios del edificio, la seguridad, la accesibilidad, las áreas de estudio y enseñanza y la tecnología, sin perder su estilo moderno de mediados del siglo XX.</x:v>
+      </x:c>
+      <x:c r="K6" s="14" t="str">
+        <x:v>Abrió: 1959; Arquitecto: Edward Durell Stone; Nuevo nombre: 1968; Gran ampliación: 1976; Siete niveles; 284,976 pies cuadrados; Renovación prevista: 2027–2032</x:v>
+      </x:c>
+      <x:c r="L6" s="14" t="str">
+        <x:v>translated_from_verified_english_human_review_recommended</x:v>
+      </x:c>
+      <x:c r="M6" s="14" t="str">
+        <x:v>2026-10-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="130" customHeight="1">
+      <x:c r="A7" s="23" t="str">
+        <x:v>usc_bldg_001_es_elementary</x:v>
+      </x:c>
+      <x:c r="B7" s="23" t="str">
+        <x:v>usc_bldg_001</x:v>
+      </x:c>
+      <x:c r="C7" s="23" t="str">
+        <x:v>es</x:v>
+      </x:c>
+      <x:c r="D7" s="23" t="str">
+        <x:v>Español</x:v>
+      </x:c>
+      <x:c r="E7" s="23" t="str">
+        <x:v>elementary</x:v>
+      </x:c>
+      <x:c r="F7" s="23" t="str">
+        <x:v>Escuela primaria</x:v>
+      </x:c>
+      <x:c r="G7" s="24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H7" s="14" t="str">
+        <x:v>Biblioteca Thomas Cooper</x:v>
+      </x:c>
+      <x:c r="I7" s="14" t="str">
+        <x:v>La Biblioteca Thomas Cooper es la biblioteca principal de la USC. Abrió en 1959 y creció mucho en 1976.</x:v>
+      </x:c>
+      <x:c r="J7" s="14" t="str">
+        <x:v>La Biblioteca Thomas Cooper abrió en 1959. Edward Durell Stone la diseñó. Al principio tenía tres pisos y espacio para unos 600 estudiantes. En 1968, la USC le dio su nombre actual. En 1976 abrieron cuatro pisos nuevos bajo tierra. La biblioteca pasó a tener siete niveles y se convirtió en la biblioteca principal de la USC. Es un ejemplo importante del diseño moderno de mediados del siglo XX. La USC planea una gran renovación entre 2027 y aproximadamente 2032. El proyecto hará que la biblioteca sea más segura y fácil de usar. También mejorará los espacios para estudiar, las aulas y la tecnología, y cuidará el aspecto especial del edificio.</x:v>
+      </x:c>
+      <x:c r="K7" s="14" t="str">
+        <x:v>Abrió: 1959; Diseñador: Edward Durell Stone; Nuevo nombre: 1968; Pisos subterráneos: 1976; Siete niveles; Renovación prevista: 2027–2032</x:v>
+      </x:c>
+      <x:c r="L7" s="14" t="str">
+        <x:v>translated_from_verified_english_human_review_recommended</x:v>
+      </x:c>
+      <x:c r="M7" s="14" t="str">
+        <x:v>2026-10-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="200" customHeight="1">
+      <x:c r="A8" s="23" t="str">
+        <x:v>usc_bldg_001_fr_college</x:v>
+      </x:c>
+      <x:c r="B8" s="23" t="str">
+        <x:v>usc_bldg_001</x:v>
+      </x:c>
+      <x:c r="C8" s="23" t="str">
+        <x:v>fr</x:v>
+      </x:c>
+      <x:c r="D8" s="23" t="str">
+        <x:v>Français</x:v>
+      </x:c>
+      <x:c r="E8" s="23" t="str">
+        <x:v>college</x:v>
+      </x:c>
+      <x:c r="F8" s="23" t="str">
+        <x:v>Niveau universitaire</x:v>
+      </x:c>
+      <x:c r="G8" s="24" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H8" s="14" t="str">
+        <x:v>Bibliothèque Thomas Cooper</x:v>
+      </x:c>
+      <x:c r="I8" s="14" t="str">
+        <x:v>Principale bibliothèque d'étude et de recherche de l'USC, inaugurée en 1959 et transformée par une extension souterraine de quatre niveaux en 1976.</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="str">
+        <x:v>La bibliothèque Thomas Cooper a ouvert en 1959 comme bibliothèque universitaire de trois niveaux conçue par Edward Durell Stone, avec deux étages hors sol, un niveau souterrain et une capacité d'environ 600 étudiants. Elle a reçu le nom de Thomas Cooper en 1968. La planification de son agrandissement a commencé en 1969, l'excavation en 1973, et une extension de quatre niveaux souterrains a ouvert en juin 1976. Le bâtiment agrandi compte sept niveaux et 284 976 pieds carrés; il a été conçu pour environ 2 500 personnes et 1,5 million de livres, et il est devenu la bibliothèque principale de l'USC. Il est considéré comme la première bibliothèque indépendante destinée aux étudiants de premier cycle dans le Sud des États-Unis et comme un exemple important du développement universitaire d'après-guerre et de l'architecture moderne du milieu du XXe siècle. En décembre 2025, l'USC a approuvé une rénovation par étapes de 65 millions de dollars. Perkins Eastman et Quackenbush Architects and Planners dirigent le projet prévu de 2027 à 2032 afin de moderniser les systèmes, la sécurité, l'accessibilité et les espaces d'étude, d'enseignement et de technologie, tout en conservant le caractère architectural du bâtiment.</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="str">
+        <x:v>Construction et ouverture : 1959; Architecte d'origine : Edward Durell Stone; Nom adopté : 1968; Extension souterraine ouverte : juin 1976; Superficie : 284 976 pieds carrés; Rénovation : 65 millions de dollars, prévue de 2027 à 2032; Concepteurs : Perkins Eastman et Quackenbush Architects and Planners</x:v>
+      </x:c>
+      <x:c r="L8" s="14" t="str">
+        <x:v>translated_from_verified_english_human_review_recommended</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="str">
+        <x:v>2026-10-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="170" customHeight="1">
+      <x:c r="A9" s="23" t="str">
+        <x:v>usc_bldg_001_fr_secondary</x:v>
+      </x:c>
+      <x:c r="B9" s="23" t="str">
+        <x:v>usc_bldg_001</x:v>
+      </x:c>
+      <x:c r="C9" s="23" t="str">
+        <x:v>fr</x:v>
+      </x:c>
+      <x:c r="D9" s="23" t="str">
+        <x:v>Français</x:v>
+      </x:c>
+      <x:c r="E9" s="23" t="str">
+        <x:v>secondary</x:v>
+      </x:c>
+      <x:c r="F9" s="23" t="str">
+        <x:v>Collège/lycée</x:v>
+      </x:c>
+      <x:c r="G9" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H9" s="14" t="str">
+        <x:v>Bibliothèque Thomas Cooper</x:v>
+      </x:c>
+      <x:c r="I9" s="14" t="str">
+        <x:v>La bibliothèque Thomas Cooper a ouvert en 1959 et est devenue la bibliothèque principale de l'USC après une grande extension souterraine ouverte en 1976.</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="str">
+        <x:v>La bibliothèque Thomas Cooper a ouvert en 1959 comme bibliothèque pour les étudiants de premier cycle. L'architecte Edward Durell Stone a conçu le bâtiment original de trois niveaux pour environ 600 étudiants. En 1968, l'USC lui a donné le nom de Thomas Cooper. Quand l'université s'est développée, une grande extension souterraine a été construite. Quatre nouveaux niveaux souterrains ont ouvert en juin 1976. La bibliothèque comptait alors sept niveaux et 284 976 pieds carrés, avec une capacité d'environ 2 500 personnes et 1,5 million de livres. Elle est devenue la bibliothèque principale de l'USC et est connue comme la première bibliothèque indépendante pour étudiants de premier cycle dans le Sud des États-Unis. En décembre 2025, l'USC a approuvé une rénovation de 65 millions de dollars. Perkins Eastman et Quackenbush Architects and Planners conçoivent le projet prévu de 2027 à 2032. Les travaux amélioreront les équipements, la sécurité, l'accessibilité, les espaces d'étude et d'enseignement et la technologie, tout en protégeant son style moderne du milieu du XXe siècle.</x:v>
+      </x:c>
+      <x:c r="K9" s="14" t="str">
+        <x:v>Ouverture : 1959; Architecte : Edward Durell Stone; Nouveau nom : 1968; Grande extension : 1976; Sept niveaux; 284 976 pieds carrés; Rénovation prévue : 2027–2032</x:v>
+      </x:c>
+      <x:c r="L9" s="14" t="str">
+        <x:v>translated_from_verified_english_human_review_recommended</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="str">
+        <x:v>2026-10-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="130" customHeight="1">
+      <x:c r="A10" s="23" t="str">
+        <x:v>usc_bldg_001_fr_elementary</x:v>
+      </x:c>
+      <x:c r="B10" s="23" t="str">
+        <x:v>usc_bldg_001</x:v>
+      </x:c>
+      <x:c r="C10" s="23" t="str">
+        <x:v>fr</x:v>
+      </x:c>
+      <x:c r="D10" s="23" t="str">
+        <x:v>Français</x:v>
+      </x:c>
+      <x:c r="E10" s="23" t="str">
+        <x:v>elementary</x:v>
+      </x:c>
+      <x:c r="F10" s="23" t="str">
+        <x:v>École primaire</x:v>
+      </x:c>
+      <x:c r="G10" s="24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H10" s="14" t="str">
+        <x:v>Bibliothèque Thomas Cooper</x:v>
+      </x:c>
+      <x:c r="I10" s="14" t="str">
+        <x:v>La bibliothèque Thomas Cooper est la bibliothèque principale de l'USC. Elle a ouvert en 1959 et est devenue beaucoup plus grande en 1976.</x:v>
+      </x:c>
+      <x:c r="J10" s="14" t="str">
+        <x:v>La bibliothèque Thomas Cooper a ouvert en 1959. Edward Durell Stone l'a conçue. Au début, elle avait trois niveaux et de la place pour environ 600 étudiants. En 1968, l'USC lui a donné son nom actuel. En 1976, quatre nouveaux niveaux ont ouvert sous terre. La bibliothèque comptait alors sept niveaux et est devenue la bibliothèque principale de l'USC. C'est un exemple important du style moderne du milieu du XXe siècle. L'USC prévoit une grande rénovation de 2027 à environ 2032. Le projet rendra la bibliothèque plus sûre et plus facile à utiliser. Il améliorera aussi les espaces d'étude, les salles de classe et la technologie, tout en gardant l'apparence particulière du bâtiment.</x:v>
+      </x:c>
+      <x:c r="K10" s="14" t="str">
+        <x:v>Ouverture : 1959; Concepteur : Edward Durell Stone; Nouveau nom : 1968; Niveaux souterrains : 1976; Sept niveaux; Rénovation prévue : 2027–2032</x:v>
+      </x:c>
+      <x:c r="L10" s="14" t="str">
+        <x:v>translated_from_verified_english_human_review_recommended</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="str">
+        <x:v>2026-10-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="200" customHeight="1">
+      <x:c r="A11" s="23" t="str">
+        <x:v>usc_bldg_002_en_college</x:v>
+      </x:c>
+      <x:c r="B11" s="23" t="str">
+        <x:v>usc_bldg_002</x:v>
+      </x:c>
+      <x:c r="C11" s="23" t="str">
+        <x:v>en</x:v>
+      </x:c>
+      <x:c r="D11" s="23" t="str">
+        <x:v>English</x:v>
+      </x:c>
+      <x:c r="E11" s="23" t="str">
+        <x:v>college</x:v>
+      </x:c>
+      <x:c r="F11" s="23" t="str">
+        <x:v>College level</x:v>
+      </x:c>
+      <x:c r="G11" s="24" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H11" s="14" t="str">
+        <x:v>President's House</x:v>
+      </x:c>
+      <x:c r="I11" s="14" t="str">
+        <x:v>USC's official presidential residence, developed from an early faculty duplex and rebuilt in 1854–1855 before its conversion in 1952.</x:v>
+      </x:c>
+      <x:c r="J11" s="14" t="str">
+        <x:v>Today's President's House occupies a site where a two-family faculty residence was built around 1810 to designs by Yates and Phillips, whose name is also recorded as Philips. In 1854–1855, the deteriorated residence was taken down to its foundation and rebuilt as a faculty duplex; P. H. Hammarskold was the architect and Clark Waring the builder. Behind it stands a brick kitchen and quarters for enslaved people built in the 1840s and associated with builder Thomas Wade. In 1952, architect J. Carroll Johnson combined and renovated the duplex as the official residence for President Donald S. Russell. It received repairs during the Horseshoe restoration in the 1970s and hosted Pope John Paul II in 1987. Every USC president since Russell has lived there. The site is historically significant because it links the university's early faculty housing, the labor and lives of enslaved people, and the modern presidency. Records differ by about a year on some early dates. It should not be confused with USC's separate 1807 President's House, which was demolished in 1939.</x:v>
+      </x:c>
+      <x:c r="K11" s="14" t="str">
+        <x:v>Original faculty residence: about 1810; Early designers: Yates and Phillips/Philips; Rebuilt: 1854–1855; Architect: P. H. Hammarskold; Builder: Clark Waring; Converted to President's House: 1952; Conversion architect: J. Carroll Johnson; Hosted Pope John Paul II: 1987</x:v>
+      </x:c>
+      <x:c r="L11" s="14" t="str">
+        <x:v>adapted_from_verified_source</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="str">
+        <x:v>2026-10-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="170" customHeight="1">
+      <x:c r="A12" s="23" t="str">
+        <x:v>usc_bldg_002_en_secondary</x:v>
+      </x:c>
+      <x:c r="B12" s="23" t="str">
+        <x:v>usc_bldg_002</x:v>
+      </x:c>
+      <x:c r="C12" s="23" t="str">
+        <x:v>en</x:v>
+      </x:c>
+      <x:c r="D12" s="23" t="str">
+        <x:v>English</x:v>
+      </x:c>
+      <x:c r="E12" s="23" t="str">
+        <x:v>secondary</x:v>
+      </x:c>
+      <x:c r="F12" s="23" t="str">
+        <x:v>Middle/High school</x:v>
+      </x:c>
+      <x:c r="G12" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H12" s="14" t="str">
+        <x:v>President's House</x:v>
+      </x:c>
+      <x:c r="I12" s="14" t="str">
+        <x:v>The President's House is USC's official presidential residence. Its history begins with faculty housing built around 1810.</x:v>
+      </x:c>
+      <x:c r="J12" s="14" t="str">
+        <x:v>A two-family home for professors was built on this site around 1810. Yates and Phillips, also spelled Philips in some records, designed it. The aging building was taken down to its foundation and rebuilt in 1854–1855. P. H. Hammarskold was the architect, and Clark Waring was the builder. A brick building behind the house served as a kitchen and living quarters for enslaved people; it dates to the 1840s and is linked to builder Thomas Wade. In 1952, architect J. Carroll Johnson joined and remodeled the duplex as the official home of President Donald S. Russell. Every USC president since Russell has lived there. Repairs were made during the Horseshoe restoration in the 1970s, and Pope John Paul II visited in 1987. The property is important because it connects the history of faculty life, slavery on campus, and the modern university presidency. Some records differ by about one year on the oldest dates.</x:v>
+      </x:c>
+      <x:c r="K12" s="14" t="str">
+        <x:v>First faculty home: about 1810; Rebuilt: 1854–1855; Architect: P. H. Hammarskold; Builder: Clark Waring; Became President's House: 1952; Conversion architect: J. Carroll Johnson; Papal visit: 1987</x:v>
+      </x:c>
+      <x:c r="L12" s="14" t="str">
+        <x:v>adapted_from_verified_source</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="str">
+        <x:v>2026-10-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="130" customHeight="1">
+      <x:c r="A13" s="23" t="str">
+        <x:v>usc_bldg_002_en_elementary</x:v>
+      </x:c>
+      <x:c r="B13" s="23" t="str">
+        <x:v>usc_bldg_002</x:v>
+      </x:c>
+      <x:c r="C13" s="23" t="str">
+        <x:v>en</x:v>
+      </x:c>
+      <x:c r="D13" s="23" t="str">
+        <x:v>English</x:v>
+      </x:c>
+      <x:c r="E13" s="23" t="str">
+        <x:v>elementary</x:v>
+      </x:c>
+      <x:c r="F13" s="23" t="str">
+        <x:v>Elementary school</x:v>
+      </x:c>
+      <x:c r="G13" s="24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H13" s="14" t="str">
+        <x:v>President's House</x:v>
+      </x:c>
+      <x:c r="I13" s="14" t="str">
+        <x:v>The President's House is the official home of USC's president. The site has been used for university housing since about 1810.</x:v>
+      </x:c>
+      <x:c r="J13" s="14" t="str">
+        <x:v>A home for two professors was built here around 1810. It was rebuilt in 1854–1855. P. H. Hammarskold was the architect, and Clark Waring was the builder. A brick building behind the house was once a kitchen and living quarters for enslaved people. It helps the university tell a fuller history of the campus. In 1952, J. Carroll Johnson changed the two-family home into one house for USC's president. Every USC president since Donald S. Russell has lived there. Pope John Paul II visited in 1987. The house is important because it connects USC's early years with the university today.</x:v>
+      </x:c>
+      <x:c r="K13" s="14" t="str">
+        <x:v>Early home: about 1810; Rebuilt: 1854–1855; Architect: P. H. Hammarskold; Became the President's House: 1952; Architect for the change: J. Carroll Johnson; Special visit: 1987</x:v>
+      </x:c>
+      <x:c r="L13" s="14" t="str">
+        <x:v>adapted_from_verified_source</x:v>
+      </x:c>
+      <x:c r="M13" s="14" t="str">
+        <x:v>2026-10-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="200" customHeight="1">
+      <x:c r="A14" s="23" t="str">
+        <x:v>usc_bldg_002_es_college</x:v>
+      </x:c>
+      <x:c r="B14" s="23" t="str">
+        <x:v>usc_bldg_002</x:v>
+      </x:c>
+      <x:c r="C14" s="23" t="str">
+        <x:v>es</x:v>
+      </x:c>
+      <x:c r="D14" s="23" t="str">
+        <x:v>Español</x:v>
+      </x:c>
+      <x:c r="E14" s="23" t="str">
+        <x:v>college</x:v>
+      </x:c>
+      <x:c r="F14" s="23" t="str">
+        <x:v>Nivel universitario</x:v>
+      </x:c>
+      <x:c r="G14" s="24" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H14" s="14" t="str">
+        <x:v>Casa del Presidente (President's House)</x:v>
+      </x:c>
+      <x:c r="I14" s="14" t="str">
+        <x:v>Residencia oficial del presidente de la USC, desarrollada a partir de una antigua vivienda doble para profesores, reconstruida en 1854–1855 y convertida en 1952.</x:v>
+      </x:c>
+      <x:c r="J14" s="14" t="str">
+        <x:v>La actual Casa del Presidente ocupa un sitio donde hacia 1810 se construyó una vivienda para dos familias de profesores, diseñada por Yates y Phillips, apellido que también aparece como Philips. En 1854–1855, la residencia deteriorada fue desmontada hasta sus cimientos y reconstruida como vivienda doble; P. H. Hammarskold fue el arquitecto y Clark Waring el constructor. Detrás se conserva un edificio de ladrillo de la década de 1840 que funcionó como cocina y vivienda de personas esclavizadas y que se relaciona con el constructor Thomas Wade. En 1952, el arquitecto J. Carroll Johnson unió y remodeló la vivienda doble como residencia oficial del presidente Donald S. Russell. Recibió reparaciones durante la restauración del Horseshoe en la década de 1970 y alojó al papa Juan Pablo II en 1987. Todos los presidentes de la USC desde Russell han vivido allí. El sitio es históricamente importante porque conecta las primeras viviendas docentes, el trabajo y la vida de las personas esclavizadas y la presidencia universitaria moderna. Algunas fuentes difieren aproximadamente un año en las fechas más antiguas. No debe confundirse con la residencia presidencial separada de 1807, demolida en 1939.</x:v>
+      </x:c>
+      <x:c r="K14" s="14" t="str">
+        <x:v>Primera vivienda docente: hacia 1810; Diseñadores: Yates y Phillips/Philips; Reconstrucción: 1854–1855; Arquitecto: P. H. Hammarskold; Constructor: Clark Waring; Conversión en Casa del Presidente: 1952; Arquitecto de la conversión: J. Carroll Johnson; Visita de Juan Pablo II: 1987</x:v>
+      </x:c>
+      <x:c r="L14" s="14" t="str">
+        <x:v>translated_from_verified_english_human_review_recommended</x:v>
+      </x:c>
+      <x:c r="M14" s="14" t="str">
+        <x:v>2026-10-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="170" customHeight="1">
+      <x:c r="A15" s="23" t="str">
+        <x:v>usc_bldg_002_es_secondary</x:v>
+      </x:c>
+      <x:c r="B15" s="23" t="str">
+        <x:v>usc_bldg_002</x:v>
+      </x:c>
+      <x:c r="C15" s="23" t="str">
+        <x:v>es</x:v>
+      </x:c>
+      <x:c r="D15" s="23" t="str">
+        <x:v>Español</x:v>
+      </x:c>
+      <x:c r="E15" s="23" t="str">
+        <x:v>secondary</x:v>
+      </x:c>
+      <x:c r="F15" s="23" t="str">
+        <x:v>Escuela intermedia/secundaria</x:v>
+      </x:c>
+      <x:c r="G15" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H15" s="14" t="str">
+        <x:v>Casa del Presidente (President's House)</x:v>
+      </x:c>
+      <x:c r="I15" s="14" t="str">
+        <x:v>La Casa del Presidente es la residencia oficial del presidente de la USC. Su historia comienza con una vivienda para profesores construida hacia 1810.</x:v>
+      </x:c>
+      <x:c r="J15" s="14" t="str">
+        <x:v>En este sitio se construyó hacia 1810 una casa para dos familias de profesores. Yates y Phillips, escrito también Philips en algunos documentos, la diseñaron. El edificio viejo fue desmontado hasta los cimientos y reconstruido en 1854–1855. P. H. Hammarskold fue el arquitecto y Clark Waring el constructor. Un edificio de ladrillo detrás de la casa sirvió como cocina y vivienda de personas esclavizadas; data de la década de 1840 y se relaciona con el constructor Thomas Wade. En 1952, el arquitecto J. Carroll Johnson unió y remodeló la vivienda doble para convertirla en el hogar oficial del presidente Donald S. Russell. Todos los presidentes de la USC desde Russell han vivido allí. Se hicieron reparaciones durante la restauración del Horseshoe en la década de 1970, y el papa Juan Pablo II la visitó en 1987. La propiedad es importante porque conecta la vida de los profesores, la historia de la esclavitud en el campus y la presidencia universitaria actual. Algunas fuentes difieren aproximadamente un año en las fechas más antiguas.</x:v>
+      </x:c>
+      <x:c r="K15" s="14" t="str">
+        <x:v>Primera vivienda: hacia 1810; Reconstrucción: 1854–1855; Arquitecto: P. H. Hammarskold; Constructor: Clark Waring; Casa del Presidente desde: 1952; Arquitecto de la conversión: J. Carroll Johnson; Visita papal: 1987</x:v>
+      </x:c>
+      <x:c r="L15" s="14" t="str">
+        <x:v>translated_from_verified_english_human_review_recommended</x:v>
+      </x:c>
+      <x:c r="M15" s="14" t="str">
+        <x:v>2026-10-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="130" customHeight="1">
+      <x:c r="A16" s="23" t="str">
+        <x:v>usc_bldg_002_es_elementary</x:v>
+      </x:c>
+      <x:c r="B16" s="23" t="str">
+        <x:v>usc_bldg_002</x:v>
+      </x:c>
+      <x:c r="C16" s="23" t="str">
+        <x:v>es</x:v>
+      </x:c>
+      <x:c r="D16" s="23" t="str">
+        <x:v>Español</x:v>
+      </x:c>
+      <x:c r="E16" s="23" t="str">
+        <x:v>elementary</x:v>
+      </x:c>
+      <x:c r="F16" s="23" t="str">
+        <x:v>Escuela primaria</x:v>
+      </x:c>
+      <x:c r="G16" s="24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H16" s="14" t="str">
+        <x:v>Casa del Presidente (President's House)</x:v>
+      </x:c>
+      <x:c r="I16" s="14" t="str">
+        <x:v>La Casa del Presidente es el hogar oficial del presidente de la USC. El sitio se usa como vivienda universitaria desde alrededor de 1810.</x:v>
+      </x:c>
+      <x:c r="J16" s="14" t="str">
+        <x:v>Hacia 1810 se construyó aquí una casa para dos profesores y sus familias. La casa fue reconstruida en 1854–1855. P. H. Hammarskold fue el arquitecto y Clark Waring fue el constructor. Un edificio de ladrillo detrás de la casa fue una cocina y vivienda de personas esclavizadas. Este lugar ayuda a contar una historia más completa del campus. En 1952, J. Carroll Johnson convirtió la vivienda para dos familias en una sola casa para el presidente de la USC. Todos los presidentes desde Donald S. Russell han vivido allí. El papa Juan Pablo II la visitó en 1987. La casa es importante porque une los primeros años de la USC con la universidad actual.</x:v>
+      </x:c>
+      <x:c r="K16" s="14" t="str">
+        <x:v>Primera casa: hacia 1810; Reconstrucción: 1854–1855; Arquitecto: P. H. Hammarskold; Casa del Presidente desde: 1952; Arquitecto del cambio: J. Carroll Johnson; Visita especial: 1987</x:v>
+      </x:c>
+      <x:c r="L16" s="14" t="str">
+        <x:v>translated_from_verified_english_human_review_recommended</x:v>
+      </x:c>
+      <x:c r="M16" s="14" t="str">
+        <x:v>2026-10-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="200" customHeight="1">
+      <x:c r="A17" s="23" t="str">
+        <x:v>usc_bldg_002_fr_college</x:v>
+      </x:c>
+      <x:c r="B17" s="23" t="str">
+        <x:v>usc_bldg_002</x:v>
+      </x:c>
+      <x:c r="C17" s="23" t="str">
+        <x:v>fr</x:v>
+      </x:c>
+      <x:c r="D17" s="23" t="str">
+        <x:v>Français</x:v>
+      </x:c>
+      <x:c r="E17" s="23" t="str">
+        <x:v>college</x:v>
+      </x:c>
+      <x:c r="F17" s="23" t="str">
+        <x:v>Niveau universitaire</x:v>
+      </x:c>
+      <x:c r="G17" s="24" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H17" s="14" t="str">
+        <x:v>Maison du président (President's House)</x:v>
+      </x:c>
+      <x:c r="I17" s="14" t="str">
+        <x:v>Résidence officielle du président de l'USC, issue d'un ancien logement double pour professeurs, reconstruit en 1854–1855 puis transformé en 1952.</x:v>
+      </x:c>
+      <x:c r="J17" s="14" t="str">
+        <x:v>L'actuelle Maison du président occupe un site où une résidence pour deux familles de professeurs a été construite vers 1810 d'après les plans de Yates et Phillips, nom également écrit Philips. En 1854–1855, la résidence délabrée a été démontée jusqu'aux fondations puis reconstruite comme logement double; P. H. Hammarskold en était l'architecte et Clark Waring le constructeur. Derrière la maison se trouve un bâtiment en brique des années 1840 qui servait de cuisine et de logement pour des personnes réduites en esclavage et qui est associé au constructeur Thomas Wade. En 1952, l'architecte J. Carroll Johnson a réuni et rénové les deux logements pour créer la résidence officielle du président Donald S. Russell. La maison a été réparée pendant la restauration du Horseshoe dans les années 1970 et a accueilli le pape Jean-Paul II en 1987. Tous les présidents de l'USC depuis Russell y ont habité. Le site est important parce qu'il relie les premiers logements du corps enseignant, le travail et la vie des personnes réduites en esclavage, et la présidence universitaire moderne. Certaines sources diffèrent d'environ un an pour les dates anciennes. Il ne faut pas le confondre avec l'ancienne résidence présidentielle distincte de 1807, démolie en 1939.</x:v>
+      </x:c>
+      <x:c r="K17" s="14" t="str">
+        <x:v>Première résidence du corps enseignant : vers 1810; Concepteurs : Yates et Phillips/Philips; Reconstruction : 1854–1855; Architecte : P. H. Hammarskold; Constructeur : Clark Waring; Transformation en Maison du président : 1952; Architecte de la transformation : J. Carroll Johnson; Visite de Jean-Paul II : 1987</x:v>
+      </x:c>
+      <x:c r="L17" s="14" t="str">
+        <x:v>translated_from_verified_english_human_review_recommended</x:v>
+      </x:c>
+      <x:c r="M17" s="14" t="str">
+        <x:v>2026-10-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="170" customHeight="1">
+      <x:c r="A18" s="23" t="str">
+        <x:v>usc_bldg_002_fr_secondary</x:v>
+      </x:c>
+      <x:c r="B18" s="23" t="str">
+        <x:v>usc_bldg_002</x:v>
+      </x:c>
+      <x:c r="C18" s="23" t="str">
+        <x:v>fr</x:v>
+      </x:c>
+      <x:c r="D18" s="23" t="str">
+        <x:v>Français</x:v>
+      </x:c>
+      <x:c r="E18" s="23" t="str">
+        <x:v>secondary</x:v>
+      </x:c>
+      <x:c r="F18" s="23" t="str">
+        <x:v>Collège/lycée</x:v>
+      </x:c>
+      <x:c r="G18" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H18" s="14" t="str">
+        <x:v>Maison du président (President's House)</x:v>
+      </x:c>
+      <x:c r="I18" s="14" t="str">
+        <x:v>La Maison du président est la résidence officielle du président de l'USC. Son histoire commence avec un logement pour professeurs construit vers 1810.</x:v>
+      </x:c>
+      <x:c r="J18" s="14" t="str">
+        <x:v>Une maison destinée à deux familles de professeurs a été construite sur ce site vers 1810. Yates et Phillips, aussi écrit Philips dans certains documents, l'ont conçue. Le bâtiment vieillissant a été démonté jusqu'aux fondations puis reconstruit en 1854–1855. P. H. Hammarskold était l'architecte et Clark Waring le constructeur. Un bâtiment en brique derrière la maison servait de cuisine et de logement à des personnes réduites en esclavage; il date des années 1840 et est lié au constructeur Thomas Wade. En 1952, l'architecte J. Carroll Johnson a réuni et rénové les deux logements pour créer la résidence officielle du président Donald S. Russell. Tous les présidents de l'USC depuis Russell y ont habité. Des réparations ont eu lieu pendant la restauration du Horseshoe dans les années 1970, et le pape Jean-Paul II y est venu en 1987. La propriété est importante car elle relie la vie du corps enseignant, l'histoire de l'esclavage sur le campus et la présidence universitaire actuelle. Certaines sources diffèrent d'environ un an pour les dates les plus anciennes.</x:v>
+      </x:c>
+      <x:c r="K18" s="14" t="str">
+        <x:v>Première maison : vers 1810; Reconstruction : 1854–1855; Architecte : P. H. Hammarskold; Constructeur : Clark Waring; Maison du président depuis : 1952; Architecte de la transformation : J. Carroll Johnson; Visite papale : 1987</x:v>
+      </x:c>
+      <x:c r="L18" s="14" t="str">
+        <x:v>translated_from_verified_english_human_review_recommended</x:v>
+      </x:c>
+      <x:c r="M18" s="14" t="str">
+        <x:v>2026-10-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="130" customHeight="1">
+      <x:c r="A19" s="23" t="str">
+        <x:v>usc_bldg_002_fr_elementary</x:v>
+      </x:c>
+      <x:c r="B19" s="23" t="str">
+        <x:v>usc_bldg_002</x:v>
+      </x:c>
+      <x:c r="C19" s="23" t="str">
+        <x:v>fr</x:v>
+      </x:c>
+      <x:c r="D19" s="23" t="str">
+        <x:v>Français</x:v>
+      </x:c>
+      <x:c r="E19" s="23" t="str">
+        <x:v>elementary</x:v>
+      </x:c>
+      <x:c r="F19" s="23" t="str">
+        <x:v>École primaire</x:v>
+      </x:c>
+      <x:c r="G19" s="24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H19" s="14" t="str">
+        <x:v>Maison du président (President's House)</x:v>
+      </x:c>
+      <x:c r="I19" s="14" t="str">
+        <x:v>La Maison du président est la résidence officielle du président de l'USC. Le site sert de logement universitaire depuis environ 1810.</x:v>
+      </x:c>
+      <x:c r="J19" s="14" t="str">
+        <x:v>Vers 1810, une maison pour deux professeurs et leurs familles a été construite ici. Elle a été reconstruite en 1854–1855. P. H. Hammarskold était l'architecte et Clark Waring le constructeur. Un bâtiment en brique derrière la maison était autrefois une cuisine et un logement pour des personnes réduites en esclavage. Ce lieu aide à raconter une histoire plus complète du campus. En 1952, J. Carroll Johnson a transformé les deux logements en une seule maison pour le président de l'USC. Tous les présidents depuis Donald S. Russell y ont habité. Le pape Jean-Paul II est venu en 1987. Cette maison est importante parce qu'elle relie les premières années de l'USC à l'université d'aujourd'hui.</x:v>
+      </x:c>
+      <x:c r="K19" s="14" t="str">
+        <x:v>Première maison : vers 1810; Reconstruction : 1854–1855; Architecte : P. H. Hammarskold; Maison du président depuis : 1952; Architecte du changement : J. Carroll Johnson; Visite spéciale : 1987</x:v>
+      </x:c>
+      <x:c r="L19" s="14" t="str">
+        <x:v>translated_from_verified_english_human_review_recommended</x:v>
+      </x:c>
+      <x:c r="M19" s="14" t="str">
+        <x:v>2026-10-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="200" customHeight="1">
+      <x:c r="A20" s="23" t="str">
+        <x:v>usc_bldg_003_en_college</x:v>
+      </x:c>
+      <x:c r="B20" s="23" t="str">
+        <x:v>usc_bldg_003</x:v>
+      </x:c>
+      <x:c r="C20" s="23" t="str">
+        <x:v>en</x:v>
+      </x:c>
+      <x:c r="D20" s="23" t="str">
+        <x:v>English</x:v>
+      </x:c>
+      <x:c r="E20" s="23" t="str">
+        <x:v>college</x:v>
+      </x:c>
+      <x:c r="F20" s="23" t="str">
+        <x:v>College level</x:v>
+      </x:c>
+      <x:c r="G20" s="24" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H20" s="14" t="str">
+        <x:v>McKissick Museum</x:v>
+      </x:c>
+      <x:c r="I20" s="14" t="str">
+        <x:v>A 1940 neoclassical former library at the head of the Horseshoe that became McKissick Museum in 1976.</x:v>
+      </x:c>
+      <x:c r="J20" s="14" t="str">
+        <x:v>McKissick Museum was built in 1940 with support from the federal Works Progress Administration and opened in 1941 as USC's main library. Architect Henry C. Hibbs designed the neoclassical building, the only twentieth-century structure on the historic Horseshoe. It was named in 1944 for university president James Rion McKissick. When the main library collections moved to the expanded Thomas Cooper Library in 1976, USC established McKissick Museum in the building; it was formally rededicated as a museum in 1984. The museum's roots extend to Thomas Cooper's mineral and gemstone collection, acquired in 1823. The 60,524-square-foot building has four principal levels, a partial basement, and a domed rotunda. Its holdings document Southern culture, history, art, and natural science. USC reports more than 46,000 cataloged cultural objects plus archival and natural-science materials, and more than 100,000 broader holdings. Exhibition spaces closed December 8, 2025, before a renovation planned for November 2026–August 2028. The project will renew building systems, safety, accessibility, classrooms, study and exhibition areas, an object-study classroom, a café, patio space, and the visitor center.</x:v>
+      </x:c>
+      <x:c r="K20" s="14" t="str">
+        <x:v>Constructed: 1940; Opened as library: 1941; Architect: Henry C. Hibbs; Named: 1944; Museum established: 1976; Rededicated: 1984; Size: 60,524 sq. ft.; Exhibition spaces closed: December 8, 2025; Renovation planned: November 2026–August 2028</x:v>
+      </x:c>
+      <x:c r="L20" s="14" t="str">
+        <x:v>adapted_from_verified_source</x:v>
+      </x:c>
+      <x:c r="M20" s="14" t="str">
+        <x:v>2026-10-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="170" customHeight="1">
+      <x:c r="A21" s="23" t="str">
+        <x:v>usc_bldg_003_en_secondary</x:v>
+      </x:c>
+      <x:c r="B21" s="23" t="str">
+        <x:v>usc_bldg_003</x:v>
+      </x:c>
+      <x:c r="C21" s="23" t="str">
+        <x:v>en</x:v>
+      </x:c>
+      <x:c r="D21" s="23" t="str">
+        <x:v>English</x:v>
+      </x:c>
+      <x:c r="E21" s="23" t="str">
+        <x:v>secondary</x:v>
+      </x:c>
+      <x:c r="F21" s="23" t="str">
+        <x:v>Middle/High school</x:v>
+      </x:c>
+      <x:c r="G21" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H21" s="14" t="str">
+        <x:v>McKissick Museum</x:v>
+      </x:c>
+      <x:c r="I21" s="14" t="str">
+        <x:v>McKissick was built in 1940, opened as USC's main library in 1941, and became a museum in 1976.</x:v>
+      </x:c>
+      <x:c r="J21" s="14" t="str">
+        <x:v>McKissick was built in 1940 with help from the federal Works Progress Administration. It opened in 1941 as USC's main library. Architect Henry C. Hibbs designed the neoclassical building, which is the only twentieth-century building on the historic Horseshoe. It was named for university president James Rion McKissick in 1944. In 1976, the main library collections moved to Thomas Cooper Library, and USC opened McKissick Museum in the building. It was formally rededicated as a museum in 1984. The museum's history connects to Thomas Cooper's mineral and gemstone collection, acquired in 1823. The building has 60,524 square feet, four main levels, a partial basement, and a domed rotunda. Its collections cover Southern culture, history, art, and natural science. Exhibition spaces closed on December 8, 2025. A renovation planned for November 2026 through August 2028 will improve building systems, safety, accessibility, classrooms, study and exhibition spaces, a hands-on object classroom, a café, patio space, and the visitor center.</x:v>
+      </x:c>
+      <x:c r="K21" s="14" t="str">
+        <x:v>Built: 1940; Opened as library: 1941; Architect: Henry C. Hibbs; Named: 1944; Museum opened: 1976; Rededicated: 1984; 60,524 sq. ft.; Renovation planned: November 2026–August 2028</x:v>
+      </x:c>
+      <x:c r="L21" s="14" t="str">
+        <x:v>adapted_from_verified_source</x:v>
+      </x:c>
+      <x:c r="M21" s="14" t="str">
+        <x:v>2026-10-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="130" customHeight="1">
+      <x:c r="A22" s="23" t="str">
+        <x:v>usc_bldg_003_en_elementary</x:v>
+      </x:c>
+      <x:c r="B22" s="23" t="str">
+        <x:v>usc_bldg_003</x:v>
+      </x:c>
+      <x:c r="C22" s="23" t="str">
+        <x:v>en</x:v>
+      </x:c>
+      <x:c r="D22" s="23" t="str">
+        <x:v>English</x:v>
+      </x:c>
+      <x:c r="E22" s="23" t="str">
+        <x:v>elementary</x:v>
+      </x:c>
+      <x:c r="F22" s="23" t="str">
+        <x:v>Elementary school</x:v>
+      </x:c>
+      <x:c r="G22" s="24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H22" s="14" t="str">
+        <x:v>McKissick Museum</x:v>
+      </x:c>
+      <x:c r="I22" s="14" t="str">
+        <x:v>McKissick opened as USC's main library in 1941. It became a museum in 1976.</x:v>
+      </x:c>
+      <x:c r="J22" s="14" t="str">
+        <x:v>McKissick was built in 1940 and opened as USC's main library in 1941. Henry C. Hibbs designed it in a classical style. It is the only building from the 1900s on the historic Horseshoe. The building was named for USC president James Rion McKissick in 1944. In 1976, the library's books moved to Thomas Cooper Library, and McKissick became a museum. The museum cares for objects about Southern culture, history, art, rocks, animals, and plants. Its exhibit rooms closed in 2025. A renovation planned for late 2026 through 2028 will make the building safer and easier to use and add better learning and exhibit spaces.</x:v>
+      </x:c>
+      <x:c r="K22" s="14" t="str">
+        <x:v>Built: 1940; Opened: 1941; Designer: Henry C. Hibbs; Named: 1944; Became a museum: 1976; Renovation planned: 2026–2028</x:v>
+      </x:c>
+      <x:c r="L22" s="14" t="str">
+        <x:v>adapted_from_verified_source</x:v>
+      </x:c>
+      <x:c r="M22" s="14" t="str">
+        <x:v>2026-10-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="200" customHeight="1">
+      <x:c r="A23" s="23" t="str">
+        <x:v>usc_bldg_003_es_college</x:v>
+      </x:c>
+      <x:c r="B23" s="23" t="str">
+        <x:v>usc_bldg_003</x:v>
+      </x:c>
+      <x:c r="C23" s="23" t="str">
+        <x:v>es</x:v>
+      </x:c>
+      <x:c r="D23" s="23" t="str">
+        <x:v>Español</x:v>
+      </x:c>
+      <x:c r="E23" s="23" t="str">
+        <x:v>college</x:v>
+      </x:c>
+      <x:c r="F23" s="23" t="str">
+        <x:v>Nivel universitario</x:v>
+      </x:c>
+      <x:c r="G23" s="24" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H23" s="14" t="str">
+        <x:v>Museo McKissick</x:v>
+      </x:c>
+      <x:c r="I23" s="14" t="str">
+        <x:v>Antigua biblioteca neoclásica construida en 1940 al comienzo del Horseshoe, convertida en el Museo McKissick en 1976.</x:v>
+      </x:c>
+      <x:c r="J23" s="14" t="str">
+        <x:v>El Museo McKissick fue construido en 1940 con apoyo de la Works Progress Administration federal y abrió en 1941 como biblioteca principal de la USC. El arquitecto Henry C. Hibbs diseñó el edificio neoclásico, la única construcción del siglo XX en el Horseshoe histórico. En 1944 recibió el nombre del presidente universitario James Rion McKissick. Cuando las colecciones de la biblioteca principal se trasladaron a la ampliada Biblioteca Thomas Cooper en 1976, la USC estableció el Museo McKissick en el edificio; en 1984 fue reinaugurado formalmente como museo. Las raíces del museo se remontan a la colección de minerales y gemas de Thomas Cooper, adquirida en 1823. El edificio de 60,524 pies cuadrados tiene cuatro niveles principales, un sótano parcial y una rotonda con cúpula. Sus colecciones documentan la cultura, la historia y el arte del sur de Estados Unidos y las ciencias naturales. La USC informa más de 46,000 objetos culturales catalogados, además de archivos y materiales de ciencias naturales, y más de 100,000 piezas en sus fondos generales. Las salas de exposición cerraron el 8 de diciembre de 2025 antes de una renovación prevista para noviembre de 2026–agosto de 2028. El proyecto renovará los sistemas, la seguridad, la accesibilidad, las aulas, las áreas de estudio y exposición, un aula para estudiar objetos, una cafetería, el patio y el centro de visitantes.</x:v>
+      </x:c>
+      <x:c r="K23" s="14" t="str">
+        <x:v>Construcción: 1940; Abrió como biblioteca: 1941; Arquitecto: Henry C. Hibbs; Nombre adoptado: 1944; Museo establecido: 1976; Reinauguración: 1984; Superficie: 60,524 pies cuadrados; Salas cerradas: 8 de diciembre de 2025; Renovación prevista: noviembre de 2026–agosto de 2028</x:v>
+      </x:c>
+      <x:c r="L23" s="14" t="str">
+        <x:v>translated_from_verified_english_human_review_recommended</x:v>
+      </x:c>
+      <x:c r="M23" s="14" t="str">
+        <x:v>2026-10-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="170" customHeight="1">
+      <x:c r="A24" s="23" t="str">
+        <x:v>usc_bldg_003_es_secondary</x:v>
+      </x:c>
+      <x:c r="B24" s="23" t="str">
+        <x:v>usc_bldg_003</x:v>
+      </x:c>
+      <x:c r="C24" s="23" t="str">
+        <x:v>es</x:v>
+      </x:c>
+      <x:c r="D24" s="23" t="str">
+        <x:v>Español</x:v>
+      </x:c>
+      <x:c r="E24" s="23" t="str">
+        <x:v>secondary</x:v>
+      </x:c>
+      <x:c r="F24" s="23" t="str">
+        <x:v>Escuela intermedia/secundaria</x:v>
+      </x:c>
+      <x:c r="G24" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H24" s="14" t="str">
+        <x:v>Museo McKissick</x:v>
+      </x:c>
+      <x:c r="I24" s="14" t="str">
+        <x:v>McKissick fue construido en 1940, abrió como biblioteca principal de la USC en 1941 y se convirtió en museo en 1976.</x:v>
+      </x:c>
+      <x:c r="J24" s="14" t="str">
+        <x:v>McKissick fue construido en 1940 con ayuda de la Works Progress Administration del gobierno federal. Abrió en 1941 como biblioteca principal de la USC. El arquitecto Henry C. Hibbs diseñó el edificio neoclásico, que es la única construcción del siglo XX en el Horseshoe histórico. En 1944 recibió el nombre del presidente universitario James Rion McKissick. En 1976, las colecciones de la biblioteca principal se trasladaron a la Biblioteca Thomas Cooper y la USC abrió el Museo McKissick en el edificio. En 1984 fue reinaugurado formalmente como museo. La historia del museo se conecta con la colección de minerales y gemas de Thomas Cooper, adquirida en 1823. El edificio tiene 60,524 pies cuadrados, cuatro niveles principales, un sótano parcial y una rotonda con cúpula. Sus colecciones tratan de la cultura, la historia y el arte del sur de Estados Unidos y de las ciencias naturales. Las salas de exposición cerraron el 8 de diciembre de 2025. Una renovación prevista para noviembre de 2026–agosto de 2028 mejorará los sistemas, la seguridad, la accesibilidad, las aulas, las áreas de estudio y exposición, un aula práctica, una cafetería, el patio y el centro de visitantes.</x:v>
+      </x:c>
+      <x:c r="K24" s="14" t="str">
+        <x:v>Construido: 1940; Abrió como biblioteca: 1941; Arquitecto: Henry C. Hibbs; Nuevo nombre: 1944; Museo desde: 1976; Reinauguración: 1984; 60,524 pies cuadrados; Renovación prevista: noviembre de 2026–agosto de 2028</x:v>
+      </x:c>
+      <x:c r="L24" s="14" t="str">
+        <x:v>translated_from_verified_english_human_review_recommended</x:v>
+      </x:c>
+      <x:c r="M24" s="14" t="str">
+        <x:v>2026-10-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="130" customHeight="1">
+      <x:c r="A25" s="23" t="str">
+        <x:v>usc_bldg_003_es_elementary</x:v>
+      </x:c>
+      <x:c r="B25" s="23" t="str">
+        <x:v>usc_bldg_003</x:v>
+      </x:c>
+      <x:c r="C25" s="23" t="str">
+        <x:v>es</x:v>
+      </x:c>
+      <x:c r="D25" s="23" t="str">
+        <x:v>Español</x:v>
+      </x:c>
+      <x:c r="E25" s="23" t="str">
+        <x:v>elementary</x:v>
+      </x:c>
+      <x:c r="F25" s="23" t="str">
+        <x:v>Escuela primaria</x:v>
+      </x:c>
+      <x:c r="G25" s="24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H25" s="14" t="str">
+        <x:v>Museo McKissick</x:v>
+      </x:c>
+      <x:c r="I25" s="14" t="str">
+        <x:v>McKissick abrió como biblioteca principal de la USC en 1941. Se convirtió en museo en 1976.</x:v>
+      </x:c>
+      <x:c r="J25" s="14" t="str">
+        <x:v>McKissick fue construido en 1940 y abrió como biblioteca principal de la USC en 1941. Henry C. Hibbs lo diseñó con un estilo clásico. Es el único edificio del siglo XX en el Horseshoe histórico. En 1944 recibió el nombre del presidente de la USC James Rion McKissick. En 1976, los libros de la biblioteca se trasladaron a la Biblioteca Thomas Cooper y McKissick se convirtió en museo. El museo cuida objetos sobre la cultura, la historia y el arte del sur de Estados Unidos, además de rocas, animales y plantas. Sus salas de exposición cerraron en 2025. Una renovación prevista desde finales de 2026 hasta 2028 hará que el edificio sea más seguro y fácil de usar y mejorará los espacios para aprender y ver exposiciones.</x:v>
+      </x:c>
+      <x:c r="K25" s="14" t="str">
+        <x:v>Construido: 1940; Abrió: 1941; Diseñador: Henry C. Hibbs; Nuevo nombre: 1944; Museo desde: 1976; Renovación prevista: 2026–2028</x:v>
+      </x:c>
+      <x:c r="L25" s="14" t="str">
+        <x:v>translated_from_verified_english_human_review_recommended</x:v>
+      </x:c>
+      <x:c r="M25" s="14" t="str">
+        <x:v>2026-10-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="200" customHeight="1">
+      <x:c r="A26" s="23" t="str">
+        <x:v>usc_bldg_003_fr_college</x:v>
+      </x:c>
+      <x:c r="B26" s="23" t="str">
+        <x:v>usc_bldg_003</x:v>
+      </x:c>
+      <x:c r="C26" s="23" t="str">
+        <x:v>fr</x:v>
+      </x:c>
+      <x:c r="D26" s="23" t="str">
+        <x:v>Français</x:v>
+      </x:c>
+      <x:c r="E26" s="23" t="str">
+        <x:v>college</x:v>
+      </x:c>
+      <x:c r="F26" s="23" t="str">
+        <x:v>Niveau universitaire</x:v>
+      </x:c>
+      <x:c r="G26" s="24" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H26" s="14" t="str">
+        <x:v>Musée McKissick</x:v>
+      </x:c>
+      <x:c r="I26" s="14" t="str">
+        <x:v>Ancienne bibliothèque néoclassique construite en 1940 à l'extrémité du Horseshoe et devenue le musée McKissick en 1976.</x:v>
+      </x:c>
+      <x:c r="J26" s="14" t="str">
+        <x:v>Le musée McKissick a été construit en 1940 avec le soutien de la Works Progress Administration fédérale et a ouvert en 1941 comme bibliothèque principale de l'USC. L'architecte Henry C. Hibbs a conçu ce bâtiment néoclassique, le seul édifice du XXe siècle sur le Horseshoe historique. En 1944, il a reçu le nom du président de l'université James Rion McKissick. Lorsque les collections de la bibliothèque principale ont été transférées à la bibliothèque Thomas Cooper agrandie en 1976, l'USC a créé le musée McKissick dans le bâtiment; celui-ci a été officiellement inauguré de nouveau comme musée en 1984. Les origines du musée remontent à la collection de minéraux et de pierres précieuses de Thomas Cooper, acquise en 1823. Le bâtiment de 60 524 pieds carrés compte quatre niveaux principaux, un sous-sol partiel et une rotonde coiffée d'un dôme. Ses collections documentent la culture, l'histoire et l'art du Sud des États-Unis ainsi que les sciences naturelles. L'USC annonce plus de 46 000 objets culturels catalogués, en plus des archives et des collections de sciences naturelles, et plus de 100 000 pièces dans l'ensemble de ses fonds. Les espaces d'exposition ont fermé le 8 décembre 2025 avant une rénovation prévue de novembre 2026 à août 2028. Le projet renouvellera les systèmes du bâtiment, la sécurité, l'accessibilité, les salles de classe, les espaces d'étude et d'exposition, une salle d'étude des objets, un café, le patio et le centre d'accueil.</x:v>
+      </x:c>
+      <x:c r="K26" s="14" t="str">
+        <x:v>Construction : 1940; Ouverture comme bibliothèque : 1941; Architecte : Henry C. Hibbs; Nom adopté : 1944; Musée créé : 1976; Nouvelle inauguration : 1984; Superficie : 60 524 pieds carrés; Espaces d'exposition fermés : 8 décembre 2025; Rénovation prévue : novembre 2026–août 2028</x:v>
+      </x:c>
+      <x:c r="L26" s="14" t="str">
+        <x:v>translated_from_verified_english_human_review_recommended</x:v>
+      </x:c>
+      <x:c r="M26" s="14" t="str">
+        <x:v>2026-10-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="170" customHeight="1">
+      <x:c r="A27" s="23" t="str">
+        <x:v>usc_bldg_003_fr_secondary</x:v>
+      </x:c>
+      <x:c r="B27" s="23" t="str">
+        <x:v>usc_bldg_003</x:v>
+      </x:c>
+      <x:c r="C27" s="23" t="str">
+        <x:v>fr</x:v>
+      </x:c>
+      <x:c r="D27" s="23" t="str">
+        <x:v>Français</x:v>
+      </x:c>
+      <x:c r="E27" s="23" t="str">
+        <x:v>secondary</x:v>
+      </x:c>
+      <x:c r="F27" s="23" t="str">
+        <x:v>Collège/lycée</x:v>
+      </x:c>
+      <x:c r="G27" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H27" s="14" t="str">
+        <x:v>Musée McKissick</x:v>
+      </x:c>
+      <x:c r="I27" s="14" t="str">
+        <x:v>McKissick a été construit en 1940, a ouvert comme bibliothèque principale de l'USC en 1941 et est devenu un musée en 1976.</x:v>
+      </x:c>
+      <x:c r="J27" s="14" t="str">
+        <x:v>McKissick a été construit en 1940 avec l'aide de la Works Progress Administration du gouvernement fédéral. Il a ouvert en 1941 comme bibliothèque principale de l'USC. L'architecte Henry C. Hibbs a conçu ce bâtiment néoclassique, le seul édifice du XXe siècle sur le Horseshoe historique. En 1944, il a reçu le nom du président de l'université James Rion McKissick. En 1976, les collections de la bibliothèque principale ont été transférées à la bibliothèque Thomas Cooper et l'USC a ouvert le musée McKissick dans le bâtiment. Celui-ci a été officiellement inauguré de nouveau comme musée en 1984. L'histoire du musée est liée à la collection de minéraux et de pierres précieuses de Thomas Cooper, acquise en 1823. Le bâtiment mesure 60 524 pieds carrés et comprend quatre niveaux principaux, un sous-sol partiel et une rotonde à dôme. Ses collections portent sur la culture, l'histoire et l'art du Sud des États-Unis et sur les sciences naturelles. Les espaces d'exposition ont fermé le 8 décembre 2025. Une rénovation prévue de novembre 2026 à août 2028 améliorera les systèmes, la sécurité, l'accessibilité, les salles de classe, les espaces d'étude et d'exposition, une salle pratique, un café, le patio et le centre d'accueil.</x:v>
+      </x:c>
+      <x:c r="K27" s="14" t="str">
+        <x:v>Construction : 1940; Ouverture comme bibliothèque : 1941; Architecte : Henry C. Hibbs; Nouveau nom : 1944; Musée depuis : 1976; Nouvelle inauguration : 1984; 60 524 pieds carrés; Rénovation prévue : novembre 2026–août 2028</x:v>
+      </x:c>
+      <x:c r="L27" s="14" t="str">
+        <x:v>translated_from_verified_english_human_review_recommended</x:v>
+      </x:c>
+      <x:c r="M27" s="14" t="str">
+        <x:v>2026-10-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="130" customHeight="1">
+      <x:c r="A28" s="23" t="str">
+        <x:v>usc_bldg_003_fr_elementary</x:v>
+      </x:c>
+      <x:c r="B28" s="23" t="str">
+        <x:v>usc_bldg_003</x:v>
+      </x:c>
+      <x:c r="C28" s="23" t="str">
+        <x:v>fr</x:v>
+      </x:c>
+      <x:c r="D28" s="23" t="str">
+        <x:v>Français</x:v>
+      </x:c>
+      <x:c r="E28" s="23" t="str">
+        <x:v>elementary</x:v>
+      </x:c>
+      <x:c r="F28" s="23" t="str">
+        <x:v>École primaire</x:v>
+      </x:c>
+      <x:c r="G28" s="24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H28" s="14" t="str">
+        <x:v>Musée McKissick</x:v>
+      </x:c>
+      <x:c r="I28" s="14" t="str">
+        <x:v>McKissick a ouvert comme bibliothèque principale de l'USC en 1941. Il est devenu un musée en 1976.</x:v>
+      </x:c>
+      <x:c r="J28" s="14" t="str">
+        <x:v>McKissick a été construit en 1940 et a ouvert comme bibliothèque principale de l'USC en 1941. Henry C. Hibbs l'a conçu dans un style classique. C'est le seul bâtiment du XXe siècle sur le Horseshoe historique. En 1944, il a reçu le nom du président de l'USC James Rion McKissick. En 1976, les livres ont été transférés à la bibliothèque Thomas Cooper et McKissick est devenu un musée. Le musée protège des objets sur la culture, l'histoire et l'art du Sud des États-Unis, ainsi que des roches, des animaux et des plantes. Ses salles d'exposition ont fermé en 2025. Une rénovation prévue de la fin de 2026 à 2028 rendra le bâtiment plus sûr et plus facile à utiliser et améliorera les espaces pour apprendre et voir des expositions.</x:v>
+      </x:c>
+      <x:c r="K28" s="14" t="str">
+        <x:v>Construction : 1940; Ouverture : 1941; Concepteur : Henry C. Hibbs; Nouveau nom : 1944; Musée depuis : 1976; Rénovation prévue : 2026–2028</x:v>
+      </x:c>
+      <x:c r="L28" s="14" t="str">
+        <x:v>translated_from_verified_english_human_review_recommended</x:v>
+      </x:c>
+      <x:c r="M28" s="14" t="str">
+        <x:v>2026-10-01</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfce36dfacaf14ac5"/>
   </x:tableParts>
 </x:worksheet>
 </file>